--- a/01_analyses_states/Uttar Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Uttar Pradesh/results/SoIB_summaries.xlsx
@@ -506,16 +506,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>18.2</v>
+        <v>23.1</v>
       </c>
       <c r="E2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -526,13 +526,13 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>18.2</v>
+        <v>15.4</v>
       </c>
       <c r="E3">
-        <v>21.3</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -540,16 +540,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>36.4</v>
+        <v>38.5</v>
       </c>
       <c r="E4">
-        <v>59.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -563,10 +563,10 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="E5">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -580,10 +580,10 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>18.2</v>
+        <v>15.4</v>
       </c>
       <c r="E6">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -602,10 +602,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C8">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +700,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -708,7 +708,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -716,7 +716,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +745,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -753,10 +753,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,10 +764,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -810,16 +810,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2">
-        <v>67.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>75.8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -847,13 +847,13 @@
         <v>33</v>
       </c>
       <c r="C4">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="D4">
         <v>22</v>
       </c>
       <c r="E4">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
     </row>
   </sheetData>
